--- a/debug/judgements_q_sty_swi/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Qwen3-4B-Instruct-2507/metrics_default_vs_simple.xlsx
+++ b/debug/judgements_q_sty_swi/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Qwen3-4B-Instruct-2507/metrics_default_vs_simple.xlsx
@@ -420,7 +420,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.5168539325842697</v>
+        <v>0.5393258426966292</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -429,16 +429,16 @@
         <v>0.4647887323943662</v>
       </c>
       <c r="D2">
-        <v>0.6229508196721312</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="E2">
         <v>89</v>
       </c>
       <c r="F2">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G2">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
